--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2184">
   <si>
     <t>en</t>
   </si>
@@ -5290,6 +5290,18 @@
     <t>Шулькер</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (Вдохновлённый)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift (Ваниль)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -6133,6 +6145,12 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
+    <t>Умамусуме</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -6404,6 +6422,12 @@
   </si>
   <si>
     <t>Зима</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Зимняя распродажа</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -6891,7 +6915,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1194"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14607,20 +14631,20 @@
         <v>1759</v>
       </c>
       <c r="B964" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B965" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B966" t="s">
         <v>1763</v>
@@ -14655,28 +14679,28 @@
         <v>1770</v>
       </c>
       <c r="B970" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B971" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="B972" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B973" t="s">
         <v>1775</v>
@@ -14727,20 +14751,20 @@
         <v>1786</v>
       </c>
       <c r="B979" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B980" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B981" t="s">
         <v>1790</v>
@@ -14847,20 +14871,20 @@
         <v>1815</v>
       </c>
       <c r="B994" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B995" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B996" t="s">
         <v>1819</v>
@@ -14879,28 +14903,28 @@
         <v>1822</v>
       </c>
       <c r="B998" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B999" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="B1000" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1001" t="s">
         <v>1827</v>
@@ -14911,20 +14935,20 @@
         <v>1828</v>
       </c>
       <c r="B1002" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1003" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1004" t="s">
         <v>1832</v>
@@ -14951,20 +14975,20 @@
         <v>1837</v>
       </c>
       <c r="B1007" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B1008" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1009" t="s">
         <v>1841</v>
@@ -14975,20 +14999,20 @@
         <v>1842</v>
       </c>
       <c r="B1010" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1011" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1012" t="s">
         <v>1846</v>
@@ -15031,28 +15055,28 @@
         <v>1855</v>
       </c>
       <c r="B1017" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1018" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="B1019" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1020" t="s">
         <v>1860</v>
@@ -15079,20 +15103,20 @@
         <v>1865</v>
       </c>
       <c r="B1023" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B1024" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B1025" t="s">
         <v>1869</v>
@@ -15143,20 +15167,20 @@
         <v>1880</v>
       </c>
       <c r="B1031" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1032" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B1033" t="s">
         <v>1884</v>
@@ -15223,68 +15247,68 @@
         <v>1899</v>
       </c>
       <c r="B1041" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1042" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1043" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1044" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="B1045" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="B1046" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="B1047" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="B1048" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B1049" t="s">
         <v>1910</v>
@@ -15303,20 +15327,20 @@
         <v>1913</v>
       </c>
       <c r="B1051" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1052" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B1053" t="s">
         <v>1917</v>
@@ -15335,20 +15359,20 @@
         <v>1920</v>
       </c>
       <c r="B1055" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1056" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1057" t="s">
         <v>1924</v>
@@ -15375,36 +15399,36 @@
         <v>1929</v>
       </c>
       <c r="B1060" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1061" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1062" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1063" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1064" t="s">
         <v>1936</v>
@@ -15487,20 +15511,20 @@
         <v>1955</v>
       </c>
       <c r="B1074" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="B1075" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="B1076" t="s">
         <v>1959</v>
@@ -15623,20 +15647,20 @@
         <v>1988</v>
       </c>
       <c r="B1091" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1092" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B1093" t="s">
         <v>1992</v>
@@ -15647,20 +15671,20 @@
         <v>1993</v>
       </c>
       <c r="B1094" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B1095" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B1096" t="s">
         <v>1997</v>
@@ -15751,20 +15775,20 @@
         <v>2018</v>
       </c>
       <c r="B1107" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B1108" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B1109" t="s">
         <v>2022</v>
@@ -15831,60 +15855,60 @@
         <v>2037</v>
       </c>
       <c r="B1117" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B1118" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="B1119" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="B1120" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="B1121" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="B1122" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="B1123" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B1124" t="s">
         <v>2047</v>
@@ -15895,44 +15919,44 @@
         <v>2048</v>
       </c>
       <c r="B1125" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B1126" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B1127" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="B1128" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="B1129" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="B1130" t="s">
         <v>2057</v>
@@ -16103,28 +16127,28 @@
         <v>2098</v>
       </c>
       <c r="B1151" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="B1152" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B1153" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="B1154" t="s">
         <v>2104</v>
@@ -16135,36 +16159,36 @@
         <v>2105</v>
       </c>
       <c r="B1155" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="B1156" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="B1157" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="B1158" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="B1159" t="s">
         <v>2112</v>
@@ -16279,140 +16303,140 @@
         <v>2139</v>
       </c>
       <c r="B1173" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="B1174" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="B1175" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="B1176" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="B1177" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="B1178" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="B1179" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B1180" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="B1181" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="B1182" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="B1183" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="B1184" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="B1185" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="B1186" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B1187" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="B1188" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="B1189" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="B1190" t="s">
         <v>2168</v>
@@ -16423,35 +16447,67 @@
         <v>2169</v>
       </c>
       <c r="B1191" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="B1192" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="B1193" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="B1194" t="s">
-        <v>2175</v>
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2183</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1194"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
